--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/179.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/179.xlsx
@@ -426,13 +426,13 @@
         <v>6.35678212706162</v>
       </c>
       <c r="E2">
-        <v>-12.98537865133231</v>
+        <v>-14.11340341274697</v>
       </c>
       <c r="F2">
-        <v>-4.196914481489772</v>
+        <v>-3.892529222596288</v>
       </c>
       <c r="G2">
-        <v>-7.42035723875695</v>
+        <v>-6.960919728816895</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>5.987698424245186</v>
       </c>
       <c r="E3">
-        <v>-13.96663557015837</v>
+        <v>-13.93740879891287</v>
       </c>
       <c r="F3">
-        <v>-3.989075443392571</v>
+        <v>-3.787094619567967</v>
       </c>
       <c r="G3">
-        <v>-6.718898986622936</v>
+        <v>-7.828044300827119</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>5.577094038631597</v>
       </c>
       <c r="E4">
-        <v>-12.80432120355764</v>
+        <v>-14.25733643060676</v>
       </c>
       <c r="F4">
-        <v>-3.896957674731655</v>
+        <v>-3.920710281639527</v>
       </c>
       <c r="G4">
-        <v>-7.232828076139395</v>
+        <v>-6.768159904247291</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>5.170071528295376</v>
       </c>
       <c r="E5">
-        <v>-12.94022976547584</v>
+        <v>-15.01786194087695</v>
       </c>
       <c r="F5">
-        <v>-3.87078126480319</v>
+        <v>-3.349374515152472</v>
       </c>
       <c r="G5">
-        <v>-7.14350624694432</v>
+        <v>-7.294592924265578</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>4.789470814072855</v>
       </c>
       <c r="E6">
-        <v>-15.93983207799459</v>
+        <v>-15.13281725356166</v>
       </c>
       <c r="F6">
-        <v>-4.454044693523156</v>
+        <v>-3.698411262159058</v>
       </c>
       <c r="G6">
-        <v>-7.065850780229635</v>
+        <v>-7.352391738835713</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>4.464887589288446</v>
       </c>
       <c r="E7">
-        <v>-14.53758557304545</v>
+        <v>-16.25860042034252</v>
       </c>
       <c r="F7">
-        <v>-3.812520528629495</v>
+        <v>-3.441062361131335</v>
       </c>
       <c r="G7">
-        <v>-6.30952354632774</v>
+        <v>-7.710546418547306</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>4.212019710279675</v>
       </c>
       <c r="E8">
-        <v>-14.70977626871311</v>
+        <v>-16.7372782368493</v>
       </c>
       <c r="F8">
-        <v>-4.178537150658665</v>
+        <v>-3.246153309824431</v>
       </c>
       <c r="G8">
-        <v>-6.502882579639952</v>
+        <v>-7.267615288666057</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>4.043179305333043</v>
       </c>
       <c r="E9">
-        <v>-17.69121487198709</v>
+        <v>-17.19854859927061</v>
       </c>
       <c r="F9">
-        <v>-3.707279763573429</v>
+        <v>-3.540397694972844</v>
       </c>
       <c r="G9">
-        <v>-5.497284508813093</v>
+        <v>-6.461527244763376</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>3.971973666623463</v>
       </c>
       <c r="E10">
-        <v>-16.45242816481882</v>
+        <v>-16.5874355604095</v>
       </c>
       <c r="F10">
-        <v>-4.007803173635062</v>
+        <v>-3.403333539403429</v>
       </c>
       <c r="G10">
-        <v>-5.681135655336519</v>
+        <v>-7.469393039284635</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>4.00003322387871</v>
       </c>
       <c r="E11">
-        <v>-16.96163242461132</v>
+        <v>-17.67838117664935</v>
       </c>
       <c r="F11">
-        <v>-3.929444587534646</v>
+        <v>-2.971532120080936</v>
       </c>
       <c r="G11">
-        <v>-4.302594697874143</v>
+        <v>-7.49553641740826</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>4.115635812490916</v>
       </c>
       <c r="E12">
-        <v>-17.8237633061916</v>
+        <v>-18.79914679422971</v>
       </c>
       <c r="F12">
-        <v>-4.249066836435223</v>
+        <v>-3.435168527060417</v>
       </c>
       <c r="G12">
-        <v>-5.497741364097513</v>
+        <v>-6.710056519487543</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>4.299641720052201</v>
       </c>
       <c r="E13">
-        <v>-18.35657902946009</v>
+        <v>-19.99018979993511</v>
       </c>
       <c r="F13">
-        <v>-4.148420196995083</v>
+        <v>-3.152593353515241</v>
       </c>
       <c r="G13">
-        <v>-5.860861862118012</v>
+        <v>-6.223793659042773</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>4.538369930085495</v>
       </c>
       <c r="E14">
-        <v>-19.02803851294741</v>
+        <v>-19.85144188481409</v>
       </c>
       <c r="F14">
-        <v>-3.520706573440897</v>
+        <v>-2.927708999370634</v>
       </c>
       <c r="G14">
-        <v>-5.953053934295636</v>
+        <v>-4.898310814938297</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>4.809407688148911</v>
       </c>
       <c r="E15">
-        <v>-19.90075696675762</v>
+        <v>-20.31640748202566</v>
       </c>
       <c r="F15">
-        <v>-3.344125979288334</v>
+        <v>-2.852215736116501</v>
       </c>
       <c r="G15">
-        <v>-6.116508809751611</v>
+        <v>-5.095089641792576</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>5.087434090964248</v>
       </c>
       <c r="E16">
-        <v>-20.18629083836326</v>
+        <v>-20.54735512794284</v>
       </c>
       <c r="F16">
-        <v>-3.303144158769634</v>
+        <v>-2.986972060101716</v>
       </c>
       <c r="G16">
-        <v>-5.469710975016503</v>
+        <v>-4.910222157788594</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>5.352910901835291</v>
       </c>
       <c r="E17">
-        <v>-20.71894353656747</v>
+        <v>-21.94096130448533</v>
       </c>
       <c r="F17">
-        <v>-2.747039583717854</v>
+        <v>-2.089146878944875</v>
       </c>
       <c r="G17">
-        <v>-3.536633776452968</v>
+        <v>-4.821141998417885</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>5.595840349649602</v>
       </c>
       <c r="E18">
-        <v>-23.56613099941006</v>
+        <v>-22.09198591264114</v>
       </c>
       <c r="F18">
-        <v>-3.370155768186503</v>
+        <v>-2.591291601378296</v>
       </c>
       <c r="G18">
-        <v>-2.906305905775734</v>
+        <v>-5.46109693552332</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>5.804694106451002</v>
       </c>
       <c r="E19">
-        <v>-22.66544016165446</v>
+        <v>-22.2596300204051</v>
       </c>
       <c r="F19">
-        <v>-2.838116922920853</v>
+        <v>-2.416063731194505</v>
       </c>
       <c r="G19">
-        <v>-4.035824317228592</v>
+        <v>-5.185907837571402</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>5.966918454229861</v>
       </c>
       <c r="E20">
-        <v>-23.51973225472747</v>
+        <v>-22.71852293397237</v>
       </c>
       <c r="F20">
-        <v>-2.671885951098868</v>
+        <v>-1.485016046980987</v>
       </c>
       <c r="G20">
-        <v>-3.054876568487146</v>
+        <v>-4.350988252567209</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>6.076462552897482</v>
       </c>
       <c r="E21">
-        <v>-25.5138412555311</v>
+        <v>-24.30174990263805</v>
       </c>
       <c r="F21">
-        <v>-2.600525412817302</v>
+        <v>-1.709810937446092</v>
       </c>
       <c r="G21">
-        <v>-4.901323411379034</v>
+        <v>-3.410657587047082</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>6.131450130965635</v>
       </c>
       <c r="E22">
-        <v>-22.62769080232652</v>
+        <v>-23.64894320358832</v>
       </c>
       <c r="F22">
-        <v>-2.348270142949394</v>
+        <v>-1.643010561716937</v>
       </c>
       <c r="G22">
-        <v>-2.964167620711116</v>
+        <v>-4.086743818168122</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>6.12847856101096</v>
       </c>
       <c r="E23">
-        <v>-22.52033879750069</v>
+        <v>-24.66552674814822</v>
       </c>
       <c r="F23">
-        <v>-2.353858309448679</v>
+        <v>-1.601597990148781</v>
       </c>
       <c r="G23">
-        <v>-3.097460115758792</v>
+        <v>-4.092166491761448</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>6.062900487415686</v>
       </c>
       <c r="E24">
-        <v>-25.87804377759799</v>
+        <v>-25.05502532602195</v>
       </c>
       <c r="F24">
-        <v>-1.904026645236853</v>
+        <v>-1.29251174624441</v>
       </c>
       <c r="G24">
-        <v>-3.292719402210546</v>
+        <v>-3.473647337022795</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>5.937483699380529</v>
       </c>
       <c r="E25">
-        <v>-25.25380269258865</v>
+        <v>-25.38493824290277</v>
       </c>
       <c r="F25">
-        <v>-2.061356809315757</v>
+        <v>-1.082566169841889</v>
       </c>
       <c r="G25">
-        <v>-3.480261807010258</v>
+        <v>-4.049145952478619</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>5.757840152997861</v>
       </c>
       <c r="E26">
-        <v>-23.67696087227378</v>
+        <v>-25.45428276538222</v>
       </c>
       <c r="F26">
-        <v>-1.675938165978217</v>
+        <v>-1.240483646409379</v>
       </c>
       <c r="G26">
-        <v>-3.502455704305532</v>
+        <v>-4.312764693770784</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>5.528189403954786</v>
       </c>
       <c r="E27">
-        <v>-26.35423999034857</v>
+        <v>-26.27509132164251</v>
       </c>
       <c r="F27">
-        <v>-1.474027753382852</v>
+        <v>-1.169577881831949</v>
       </c>
       <c r="G27">
-        <v>-4.700734146609053</v>
+        <v>-4.259521189862685</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>5.250957479244196</v>
       </c>
       <c r="E28">
-        <v>-24.61377987566257</v>
+        <v>-25.54798594954893</v>
       </c>
       <c r="F28">
-        <v>-1.078141031176134</v>
+        <v>-1.541343373636548</v>
       </c>
       <c r="G28">
-        <v>-2.857462116889327</v>
+        <v>-3.999342105385824</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>4.935361146144559</v>
       </c>
       <c r="E29">
-        <v>-24.76023978201865</v>
+        <v>-23.76736732736291</v>
       </c>
       <c r="F29">
-        <v>-1.986385417525388</v>
+        <v>-0.7827443869704278</v>
       </c>
       <c r="G29">
-        <v>-4.195369438402688</v>
+        <v>-4.175777629901281</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>4.59179876142596</v>
       </c>
       <c r="E30">
-        <v>-24.7084340393709</v>
+        <v>-24.87413090331156</v>
       </c>
       <c r="F30">
-        <v>-1.500244753314053</v>
+        <v>-1.161857497637858</v>
       </c>
       <c r="G30">
-        <v>-3.67276009848226</v>
+        <v>-4.688240147743843</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>4.228763420449187</v>
       </c>
       <c r="E31">
-        <v>-23.28547882278469</v>
+        <v>-25.98366137687889</v>
       </c>
       <c r="F31">
-        <v>-1.549699115628586</v>
+        <v>-1.00266516363746</v>
       </c>
       <c r="G31">
-        <v>-3.201265581688179</v>
+        <v>-5.313906770301783</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>3.852641165240621</v>
       </c>
       <c r="E32">
-        <v>-23.75216976859317</v>
+        <v>-24.81887446346996</v>
       </c>
       <c r="F32">
-        <v>-1.586238401766073</v>
+        <v>-1.087138757905342</v>
       </c>
       <c r="G32">
-        <v>-4.166084352562295</v>
+        <v>-4.842673786605305</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>3.476223515243423</v>
       </c>
       <c r="E33">
-        <v>-23.15133636572948</v>
+        <v>-24.06433559583792</v>
       </c>
       <c r="F33">
-        <v>-1.64216231349647</v>
+        <v>-1.229689190783498</v>
       </c>
       <c r="G33">
-        <v>-4.173503285115802</v>
+        <v>-3.793505625936098</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>3.111320430889837</v>
       </c>
       <c r="E34">
-        <v>-24.58591164661937</v>
+        <v>-23.99287627599688</v>
       </c>
       <c r="F34">
-        <v>-1.232714388538522</v>
+        <v>-0.9078734250003071</v>
       </c>
       <c r="G34">
-        <v>-4.866579235944382</v>
+        <v>-3.954467660601003</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>2.767014216258356</v>
       </c>
       <c r="E35">
-        <v>-23.17894647175424</v>
+        <v>-23.04881171419582</v>
       </c>
       <c r="F35">
-        <v>-1.13611515222846</v>
+        <v>-1.129252956663669</v>
       </c>
       <c r="G35">
-        <v>-4.210856170435399</v>
+        <v>-4.398981231250024</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>2.449377915855734</v>
       </c>
       <c r="E36">
-        <v>-22.13195875270685</v>
+        <v>-24.07160832509424</v>
       </c>
       <c r="F36">
-        <v>-1.390337794678018</v>
+        <v>-1.192343074795685</v>
       </c>
       <c r="G36">
-        <v>-3.649675664436922</v>
+        <v>-4.690918379085113</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>2.169775673606933</v>
       </c>
       <c r="E37">
-        <v>-23.50189006713725</v>
+        <v>-22.57628356539145</v>
       </c>
       <c r="F37">
-        <v>-1.960184984942242</v>
+        <v>-1.278717772252993</v>
       </c>
       <c r="G37">
-        <v>-5.302445661644827</v>
+        <v>-4.566044601343805</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>1.934618996396722</v>
       </c>
       <c r="E38">
-        <v>-20.71844993290064</v>
+        <v>-21.17862893308609</v>
       </c>
       <c r="F38">
-        <v>-1.354432209603673</v>
+        <v>-1.267601910074826</v>
       </c>
       <c r="G38">
-        <v>-4.179922432916449</v>
+        <v>-4.603563013940365</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>1.745129202540948</v>
       </c>
       <c r="E39">
-        <v>-21.77116617156774</v>
+        <v>-20.88758390861312</v>
       </c>
       <c r="F39">
-        <v>-0.9395518512181658</v>
+        <v>-1.294140316558314</v>
       </c>
       <c r="G39">
-        <v>-4.465804592960212</v>
+        <v>-4.324315187157301</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>1.59758396410753</v>
       </c>
       <c r="E40">
-        <v>-19.83954558359594</v>
+        <v>-21.0534709684621</v>
       </c>
       <c r="F40">
-        <v>-1.640118731113764</v>
+        <v>-0.9171229754199663</v>
       </c>
       <c r="G40">
-        <v>-4.143976529451042</v>
+        <v>-4.501204256411639</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>1.492379221117611</v>
       </c>
       <c r="E41">
-        <v>-19.30448373721965</v>
+        <v>-20.87793373050277</v>
       </c>
       <c r="F41">
-        <v>-1.241534844643531</v>
+        <v>-0.5973234558951892</v>
       </c>
       <c r="G41">
-        <v>-2.473276617602445</v>
+        <v>-4.82152602170044</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.425691068916157</v>
       </c>
       <c r="E42">
-        <v>-21.38563000845071</v>
+        <v>-19.4418957525084</v>
       </c>
       <c r="F42">
-        <v>-1.241210952989036</v>
+        <v>-1.471918729975324</v>
       </c>
       <c r="G42">
-        <v>-4.253310606431013</v>
+        <v>-4.463854681637581</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>1.392271475990144</v>
       </c>
       <c r="E43">
-        <v>-18.2401655481449</v>
+        <v>-20.29333943543058</v>
       </c>
       <c r="F43">
-        <v>-1.12398619671667</v>
+        <v>-0.885683119014114</v>
       </c>
       <c r="G43">
-        <v>-3.518776693814139</v>
+        <v>-3.738901487811359</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>1.385816912885889</v>
       </c>
       <c r="E44">
-        <v>-17.98837786484442</v>
+        <v>-19.21210286746318</v>
       </c>
       <c r="F44">
-        <v>-1.435622983854261</v>
+        <v>-1.189366750717427</v>
       </c>
       <c r="G44">
-        <v>-4.759039474646697</v>
+        <v>-4.340503754844337</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>1.403901220118738</v>
       </c>
       <c r="E45">
-        <v>-17.93173118348248</v>
+        <v>-18.90475533656259</v>
       </c>
       <c r="F45">
-        <v>-1.285135962889883</v>
+        <v>-1.029307116046298</v>
       </c>
       <c r="G45">
-        <v>-4.99127424422657</v>
+        <v>-3.85876972069729</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.439824455212101</v>
       </c>
       <c r="E46">
-        <v>-17.7559267655567</v>
+        <v>-16.98589145987041</v>
       </c>
       <c r="F46">
-        <v>-1.341792979771758</v>
+        <v>-1.228589118872581</v>
       </c>
       <c r="G46">
-        <v>-4.543801045865441</v>
+        <v>-4.090882000092211</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.485306925989209</v>
       </c>
       <c r="E47">
-        <v>-16.06182011081321</v>
+        <v>-17.39916452628441</v>
       </c>
       <c r="F47">
-        <v>-1.105808502429638</v>
+        <v>-0.985143536333445</v>
       </c>
       <c r="G47">
-        <v>-3.983428312978547</v>
+        <v>-5.169590158608335</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.531900670812808</v>
       </c>
       <c r="E48">
-        <v>-16.40947106038206</v>
+        <v>-18.72903243116895</v>
       </c>
       <c r="F48">
-        <v>-1.526370632830947</v>
+        <v>-1.243941251948664</v>
       </c>
       <c r="G48">
-        <v>-3.552497910677156</v>
+        <v>-5.05409515637978</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.573985268761508</v>
       </c>
       <c r="E49">
-        <v>-16.01806146647709</v>
+        <v>-17.15938635605227</v>
       </c>
       <c r="F49">
-        <v>-1.444353147912365</v>
+        <v>-0.9413684609325051</v>
       </c>
       <c r="G49">
-        <v>-5.444501170734953</v>
+        <v>-4.158632314553396</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>1.604027891074556</v>
       </c>
       <c r="E50">
-        <v>-15.06858084976285</v>
+        <v>-16.17229676270433</v>
       </c>
       <c r="F50">
-        <v>-1.773054303547626</v>
+        <v>-1.12669661485863</v>
       </c>
       <c r="G50">
-        <v>-4.097377290440261</v>
+        <v>-4.941053268395827</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>1.614778709231087</v>
       </c>
       <c r="E51">
-        <v>-15.35752013382226</v>
+        <v>-15.41779865133836</v>
       </c>
       <c r="F51">
-        <v>-1.519180403774647</v>
+        <v>-1.410805924833791</v>
       </c>
       <c r="G51">
-        <v>-4.916386393582717</v>
+        <v>-4.688816182667677</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>1.600513216396531</v>
       </c>
       <c r="E52">
-        <v>-12.05931930218575</v>
+        <v>-14.79293263691596</v>
       </c>
       <c r="F52">
-        <v>-1.716744372607524</v>
+        <v>-1.146085382288555</v>
       </c>
       <c r="G52">
-        <v>-5.770672669991647</v>
+        <v>-4.743542810977369</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>1.558098259642781</v>
       </c>
       <c r="E53">
-        <v>-13.82251688486426</v>
+        <v>-15.090507720908</v>
       </c>
       <c r="F53">
-        <v>-1.539941775991011</v>
+        <v>-1.056170242551683</v>
       </c>
       <c r="G53">
-        <v>-4.957082929896978</v>
+        <v>-5.835791100749111</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>1.484709392516945</v>
       </c>
       <c r="E54">
-        <v>-14.16566653126949</v>
+        <v>-15.53371852898671</v>
       </c>
       <c r="F54">
-        <v>-1.933779117243202</v>
+        <v>-1.10744535641757</v>
       </c>
       <c r="G54">
-        <v>-6.501737130883364</v>
+        <v>-6.109023666287319</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>1.379171891025446</v>
       </c>
       <c r="E55">
-        <v>-12.48397695225504</v>
+        <v>-13.49563351709459</v>
       </c>
       <c r="F55">
-        <v>-0.5617707553344373</v>
+        <v>-1.220721285280791</v>
       </c>
       <c r="G55">
-        <v>-5.503389154787509</v>
+        <v>-5.792214389815684</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>1.241916931481792</v>
       </c>
       <c r="E56">
-        <v>-12.99156454682679</v>
+        <v>-14.50652476982684</v>
       </c>
       <c r="F56">
-        <v>-1.245675024922723</v>
+        <v>-1.340985321554029</v>
       </c>
       <c r="G56">
-        <v>-5.458057854718269</v>
+        <v>-5.716939205343737</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>1.075703846545603</v>
       </c>
       <c r="E57">
-        <v>-12.29067451076362</v>
+        <v>-12.97145359375873</v>
       </c>
       <c r="F57">
-        <v>-1.845946493156968</v>
+        <v>-0.8718700925724322</v>
       </c>
       <c r="G57">
-        <v>-6.926413912661072</v>
+        <v>-6.099293972947401</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.8840109770780652</v>
       </c>
       <c r="E58">
-        <v>-11.49729039309378</v>
+        <v>-13.08778556254177</v>
       </c>
       <c r="F58">
-        <v>-0.6869776599001798</v>
+        <v>-1.220804122021071</v>
       </c>
       <c r="G58">
-        <v>-6.037605267368622</v>
+        <v>-6.7882913316716</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.6722252199538877</v>
       </c>
       <c r="E59">
-        <v>-11.56743192699859</v>
+        <v>-13.65993561104088</v>
       </c>
       <c r="F59">
-        <v>-0.9367668800099539</v>
+        <v>-1.364673315804483</v>
       </c>
       <c r="G59">
-        <v>-5.516896180587736</v>
+        <v>-5.877153056716765</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.445894089669252</v>
       </c>
       <c r="E60">
-        <v>-11.52060297728527</v>
+        <v>-12.88918027798737</v>
       </c>
       <c r="F60">
-        <v>-1.206870982305983</v>
+        <v>-1.053787029533829</v>
       </c>
       <c r="G60">
-        <v>-5.924977197577077</v>
+        <v>-5.956880924939034</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.2118466611225146</v>
       </c>
       <c r="E61">
-        <v>-11.44326116970826</v>
+        <v>-11.71140117265044</v>
       </c>
       <c r="F61">
-        <v>-1.629275401811118</v>
+        <v>-1.547147744027964</v>
       </c>
       <c r="G61">
-        <v>-6.730538864739014</v>
+        <v>-5.787599489333941</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.02369450283894622</v>
       </c>
       <c r="E62">
-        <v>-11.31048631180337</v>
+        <v>-12.72190297661804</v>
       </c>
       <c r="F62">
-        <v>-1.271334533591841</v>
+        <v>-1.577225764423614</v>
       </c>
       <c r="G62">
-        <v>-6.565276431418596</v>
+        <v>-6.266185194673141</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.2541225251966249</v>
       </c>
       <c r="E63">
-        <v>-10.75718377212418</v>
+        <v>-13.44945666763837</v>
       </c>
       <c r="F63">
-        <v>-1.599841022887443</v>
+        <v>-1.448195944293952</v>
       </c>
       <c r="G63">
-        <v>-6.507878192858712</v>
+        <v>-5.565448641466687</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.4744778672071978</v>
       </c>
       <c r="E64">
-        <v>-10.93634378928965</v>
+        <v>-12.00065292141638</v>
       </c>
       <c r="F64">
-        <v>-1.401583710538424</v>
+        <v>-1.298905085859217</v>
       </c>
       <c r="G64">
-        <v>-6.704723230623777</v>
+        <v>-6.221016111335325</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.6802903129076737</v>
       </c>
       <c r="E65">
-        <v>-10.92337423973168</v>
+        <v>-12.31594792420043</v>
       </c>
       <c r="F65">
-        <v>-1.427076717359578</v>
+        <v>-1.860082582885742</v>
       </c>
       <c r="G65">
-        <v>-6.482655146395005</v>
+        <v>-5.631086827873816</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.8686012470990475</v>
       </c>
       <c r="E66">
-        <v>-10.08105090346094</v>
+        <v>-12.32765402951026</v>
       </c>
       <c r="F66">
-        <v>-1.724136723310106</v>
+        <v>-1.377752408727285</v>
       </c>
       <c r="G66">
-        <v>-6.184785500953541</v>
+        <v>-5.872273312591879</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.037036041836362</v>
       </c>
       <c r="E67">
-        <v>-9.68064776017674</v>
+        <v>-12.2277875922191</v>
       </c>
       <c r="F67">
-        <v>-1.425301526015379</v>
+        <v>-1.651517066576285</v>
       </c>
       <c r="G67">
-        <v>-5.356874340855984</v>
+        <v>-5.837155045511291</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.185188037377959</v>
       </c>
       <c r="E68">
-        <v>-10.34893731185869</v>
+        <v>-11.96620934811404</v>
       </c>
       <c r="F68">
-        <v>-2.253069190815258</v>
+        <v>-1.666899849246272</v>
       </c>
       <c r="G68">
-        <v>-6.05842197771956</v>
+        <v>-5.430120160912359</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.313393755402031</v>
       </c>
       <c r="E69">
-        <v>-10.25830896154319</v>
+        <v>-11.61153473535929</v>
       </c>
       <c r="F69">
-        <v>-1.279491467407207</v>
+        <v>-1.618090785138519</v>
       </c>
       <c r="G69">
-        <v>-6.363694002986834</v>
+        <v>-5.968563840147121</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.422669299065053</v>
       </c>
       <c r="E70">
-        <v>-9.77027984621056</v>
+        <v>-10.99955222948871</v>
       </c>
       <c r="F70">
-        <v>-1.675017021426304</v>
+        <v>-1.433733477808475</v>
       </c>
       <c r="G70">
-        <v>-6.211812794736151</v>
+        <v>-6.112853967476256</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.513911328399073</v>
       </c>
       <c r="E71">
-        <v>-9.745753630985016</v>
+        <v>-11.8401411602145</v>
       </c>
       <c r="F71">
-        <v>-1.605772133491488</v>
+        <v>-1.880773543872868</v>
       </c>
       <c r="G71">
-        <v>-5.436896847631247</v>
+        <v>-5.220840714101792</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.588980916686203</v>
       </c>
       <c r="E72">
-        <v>-9.820853843928221</v>
+        <v>-12.462113479746</v>
       </c>
       <c r="F72">
-        <v>-2.205952481311425</v>
+        <v>-1.42580765849849</v>
       </c>
       <c r="G72">
-        <v>-6.118296504342818</v>
+        <v>-6.178270347332255</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.648909141551988</v>
       </c>
       <c r="E73">
-        <v>-10.32842785307795</v>
+        <v>-12.49371769984553</v>
       </c>
       <c r="F73">
-        <v>-1.671712663856537</v>
+        <v>-1.70357581600522</v>
       </c>
       <c r="G73">
-        <v>-5.430623363834329</v>
+        <v>-5.47903678180063</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.693355386449905</v>
       </c>
       <c r="E74">
-        <v>-10.1862292407631</v>
+        <v>-11.28319319895914</v>
       </c>
       <c r="F74">
-        <v>-2.267780167521574</v>
+        <v>-2.087203529017907</v>
       </c>
       <c r="G74">
-        <v>-5.32060069338219</v>
+        <v>-4.672776589529907</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.720978952299807</v>
       </c>
       <c r="E75">
-        <v>-11.78214046512426</v>
+        <v>-12.83663639407637</v>
       </c>
       <c r="F75">
-        <v>-1.977354556100068</v>
+        <v>-1.843444823600514</v>
       </c>
       <c r="G75">
-        <v>-5.387109553266148</v>
+        <v>-4.821098961325874</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.731533598316094</v>
       </c>
       <c r="E76">
-        <v>-10.93208702372243</v>
+        <v>-13.41854530406201</v>
       </c>
       <c r="F76">
-        <v>-2.474940772715883</v>
+        <v>-2.152148361764791</v>
       </c>
       <c r="G76">
-        <v>-4.981753115255627</v>
+        <v>-5.369676220456346</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.724142567882315</v>
       </c>
       <c r="E77">
-        <v>-11.82333146469803</v>
+        <v>-13.13455564209299</v>
       </c>
       <c r="F77">
-        <v>-2.526799885600743</v>
+        <v>-2.719671981464163</v>
       </c>
       <c r="G77">
-        <v>-4.764154267504871</v>
+        <v>-4.89234190133099</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.697854507923795</v>
       </c>
       <c r="E78">
-        <v>-11.66448618193098</v>
+        <v>-13.85326069490234</v>
       </c>
       <c r="F78">
-        <v>-2.629015452901785</v>
+        <v>-2.471685288822881</v>
       </c>
       <c r="G78">
-        <v>-5.136971353409896</v>
+        <v>-4.944208218294752</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.651915123556678</v>
       </c>
       <c r="E79">
-        <v>-11.55136037274536</v>
+        <v>-13.79247951677139</v>
       </c>
       <c r="F79">
-        <v>-2.212613383597336</v>
+        <v>-2.85192829262773</v>
       </c>
       <c r="G79">
-        <v>-4.104081145157285</v>
+        <v>-4.876060638368855</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.588012892257497</v>
       </c>
       <c r="E80">
-        <v>-12.4253875555438</v>
+        <v>-13.71638303954649</v>
       </c>
       <c r="F80">
-        <v>-2.983713262739103</v>
+        <v>-2.345941602180124</v>
       </c>
       <c r="G80">
-        <v>-3.861173176758801</v>
+        <v>-4.257832811637657</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.507349889650523</v>
       </c>
       <c r="E81">
-        <v>-13.41181599168662</v>
+        <v>-15.235156237661</v>
       </c>
       <c r="F81">
-        <v>-3.134726297004259</v>
+        <v>-2.723151124555921</v>
       </c>
       <c r="G81">
-        <v>-4.503885798298449</v>
+        <v>-4.270757181422971</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.411156873996517</v>
       </c>
       <c r="E82">
-        <v>-15.78231816658579</v>
+        <v>-16.73805713437863</v>
       </c>
       <c r="F82">
-        <v>-3.115240610588206</v>
+        <v>-2.856926661536222</v>
       </c>
       <c r="G82">
-        <v>-3.42451884122001</v>
+        <v>-4.107702881977248</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.30063931124145</v>
       </c>
       <c r="E83">
-        <v>-15.17791632620405</v>
+        <v>-17.05391366793963</v>
       </c>
       <c r="F83">
-        <v>-3.574333422363331</v>
+        <v>-2.559943693754154</v>
       </c>
       <c r="G83">
-        <v>-3.696519883817609</v>
+        <v>-3.885009104641554</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.178795551596549</v>
       </c>
       <c r="E84">
-        <v>-15.01744532126824</v>
+        <v>-18.32287359742099</v>
       </c>
       <c r="F84">
-        <v>-2.807222960633446</v>
+        <v>-3.12747145529054</v>
       </c>
       <c r="G84">
-        <v>-4.229878565104051</v>
+        <v>-4.263285280140837</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.047362686315355</v>
       </c>
       <c r="E85">
-        <v>-16.26528897645185</v>
+        <v>-17.62231866843439</v>
       </c>
       <c r="F85">
-        <v>-2.982392016731638</v>
+        <v>-2.957774594255242</v>
       </c>
       <c r="G85">
-        <v>-2.981054713506938</v>
+        <v>-4.418486965567409</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.9081582263463137</v>
       </c>
       <c r="E86">
-        <v>-17.86235949015897</v>
+        <v>-18.93448929689695</v>
       </c>
       <c r="F86">
-        <v>-3.126002759885377</v>
+        <v>-2.841864457051118</v>
       </c>
       <c r="G86">
-        <v>-4.446788819382639</v>
+        <v>-3.732121490546932</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.7629981588811361</v>
       </c>
       <c r="E87">
-        <v>-18.69595645701693</v>
+        <v>-18.82637650843783</v>
       </c>
       <c r="F87">
-        <v>-3.390922938974687</v>
+        <v>-3.102883025673242</v>
       </c>
       <c r="G87">
-        <v>-3.674418681797435</v>
+        <v>-3.359367305007153</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.6150503963248316</v>
       </c>
       <c r="E88">
-        <v>-18.49186266196523</v>
+        <v>-20.54269532818894</v>
       </c>
       <c r="F88">
-        <v>-3.764571309885849</v>
+        <v>-3.190598849955682</v>
       </c>
       <c r="G88">
-        <v>-3.601921045032935</v>
+        <v>-3.991204784450295</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.466554920399094</v>
       </c>
       <c r="E89">
-        <v>-20.29203976339038</v>
+        <v>-22.10538113875583</v>
       </c>
       <c r="F89">
-        <v>-3.330656725318814</v>
+        <v>-3.262458065413734</v>
       </c>
       <c r="G89">
-        <v>-4.188658962594586</v>
+        <v>-3.814355441742428</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.3202287966447415</v>
       </c>
       <c r="E90">
-        <v>-21.83365911287359</v>
+        <v>-23.2779298566139</v>
       </c>
       <c r="F90">
-        <v>-4.170401754395771</v>
+        <v>-3.447343871146764</v>
       </c>
       <c r="G90">
-        <v>-3.503561426515649</v>
+        <v>-4.358880593132832</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.1792033696285027</v>
       </c>
       <c r="E91">
-        <v>-25.01105837188149</v>
+        <v>-24.11959203567951</v>
       </c>
       <c r="F91">
-        <v>-4.010012429498328</v>
+        <v>-3.485126536755852</v>
       </c>
       <c r="G91">
-        <v>-4.207456240166567</v>
+        <v>-4.433132819033145</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.04765097155040231</v>
       </c>
       <c r="E92">
-        <v>-26.88068415068827</v>
+        <v>-27.0175527490961</v>
       </c>
       <c r="F92">
-        <v>-3.789236777671606</v>
+        <v>-3.43266023056474</v>
       </c>
       <c r="G92">
-        <v>-4.268035912989691</v>
+        <v>-4.53631259185561</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.07131084360716343</v>
       </c>
       <c r="E93">
-        <v>-27.83094819340583</v>
+        <v>-27.59875068866253</v>
       </c>
       <c r="F93">
-        <v>-3.628376940089373</v>
+        <v>-3.207994565414472</v>
       </c>
       <c r="G93">
-        <v>-4.677186236188216</v>
+        <v>-4.952782531241464</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.1752275332961701</v>
       </c>
       <c r="E94">
-        <v>-29.52913953170424</v>
+        <v>-29.85838902714292</v>
       </c>
       <c r="F94">
-        <v>-3.877720498536442</v>
+        <v>-3.775729418801558</v>
       </c>
       <c r="G94">
-        <v>-4.875699788905075</v>
+        <v>-5.03837999670486</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.2622877845173492</v>
       </c>
       <c r="E95">
-        <v>-31.85708763635333</v>
+        <v>-30.20368743446479</v>
       </c>
       <c r="F95">
-        <v>-3.201002316167441</v>
+        <v>-4.002368255105294</v>
       </c>
       <c r="G95">
-        <v>-5.609127979311831</v>
+        <v>-5.233751841704949</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.3317545809461478</v>
       </c>
       <c r="E96">
-        <v>-33.18582115849895</v>
+        <v>-32.59698594751858</v>
       </c>
       <c r="F96">
-        <v>-4.223838078815562</v>
+        <v>-3.574214137457328</v>
       </c>
       <c r="G96">
-        <v>-4.403423983363726</v>
+        <v>-5.427955064129676</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.3836957332051766</v>
       </c>
       <c r="E97">
-        <v>-33.86267631876641</v>
+        <v>-34.46204249605162</v>
       </c>
       <c r="F97">
-        <v>-4.426759928009745</v>
+        <v>-3.738510871393776</v>
       </c>
       <c r="G97">
-        <v>-6.198885114405297</v>
+        <v>-6.202367808312609</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.4201374014105649</v>
       </c>
       <c r="E98">
-        <v>-37.80225624529429</v>
+        <v>-36.95321265359618</v>
       </c>
       <c r="F98">
-        <v>-4.337481802805626</v>
+        <v>-4.019544453202342</v>
       </c>
       <c r="G98">
-        <v>-5.625379447364113</v>
+        <v>-6.587622613808676</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.4414767149489183</v>
       </c>
       <c r="E99">
-        <v>-39.57912302676496</v>
+        <v>-39.47704669415806</v>
       </c>
       <c r="F99">
-        <v>-4.613101175269494</v>
+        <v>-3.891784520301171</v>
       </c>
       <c r="G99">
-        <v>-6.102564791940202</v>
+        <v>-6.815166340359402</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.4515216709377489</v>
       </c>
       <c r="E100">
-        <v>-41.35427351658672</v>
+        <v>-42.16104606766024</v>
       </c>
       <c r="F100">
-        <v>-4.401853405309772</v>
+        <v>-3.945911703134897</v>
       </c>
       <c r="G100">
-        <v>-6.85174455802281</v>
+        <v>-7.332882693972788</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>0.4493906456881935</v>
       </c>
       <c r="E101">
-        <v>-45.65018774159317</v>
+        <v>-43.18325850541167</v>
       </c>
       <c r="F101">
-        <v>-4.618863298923367</v>
+        <v>-3.973469001523828</v>
       </c>
       <c r="G101">
-        <v>-6.110483616870138</v>
+        <v>-7.612517854583947</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.4417647132384941</v>
       </c>
       <c r="E102">
-        <v>-44.96577908668092</v>
+        <v>-46.05421592832052</v>
       </c>
       <c r="F102">
-        <v>-4.977407218611883</v>
+        <v>-3.986452003827905</v>
       </c>
       <c r="G102">
-        <v>-7.117806481922957</v>
+        <v>-7.553580212348302</v>
       </c>
     </row>
   </sheetData>
